--- a/assessment_forms/024_group_class_popularity_assessment_form--assessment_forms.xlsx
+++ b/assessment_forms/024_group_class_popularity_assessment_form--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Class Frequency</t>
+          <t>Class Frequency (2)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>class_revenue</t>
+          <t>class_revenue_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Class Revenue</t>
+          <t>Class Revenue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>class_capacity</t>
+          <t>class_capacity_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Class Capacity</t>
+          <t>Class Capacity 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>member_satisfaction</t>
+          <t>member_satisfaction_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Member Satisfaction</t>
+          <t>Member Satisfaction 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>staff_satisfaction</t>
+          <t>staff_satisfaction_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Staff Satisfaction</t>
+          <t>Staff Satisfaction 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1216,29 +1216,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fitness_class_frequency_choices</t>
+          <t>preferred_time_of_day_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>morning</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1267,29 +1267,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>afternoon</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>preferred_time_of_day_choices</t>
+          <t>preferred_day_of_week_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>evening</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>monday</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>tuesday</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wednesday</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>thursday</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>friday</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1386,29 +1386,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>saturday</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>preferred_day_of_week_choices</t>
+          <t>preferred_duration_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sunday</t>
+          <t>30min</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>30min</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>30min</t>
+          <t>45min</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>30min</t>
+          <t>45min</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>45min</t>
+          <t>60min</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>45min</t>
+          <t>60min</t>
         </is>
       </c>
     </row>
@@ -1454,29 +1454,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>60min</t>
+          <t>90min</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>60min</t>
+          <t>90min</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>preferred_duration_choices</t>
+          <t>class_demand_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>90min</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>90min</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1505,29 +1505,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>class_demand_choices</t>
+          <t>class_suggested_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1539,29 +1539,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>class_suggested_choices</t>
+          <t>member_satisfaction_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1590,199 +1590,199 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>member_satisfaction_choices</t>
+          <t>staff_satisfaction_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>member_satisfaction_choices</t>
+          <t>staff_satisfaction_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>member_satisfaction_choices</t>
+          <t>staff_satisfaction_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>staff_satisfaction_choices</t>
+          <t>class_time_of_day_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>staff_satisfaction_choices</t>
+          <t>class_time_of_day_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>staff_satisfaction_choices</t>
+          <t>class_time_of_day_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>staff_satisfaction_choices</t>
+          <t>class_day_of_week_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>staff_satisfaction_choices</t>
+          <t>class_day_of_week_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>class_time_of_day_choices</t>
+          <t>class_day_of_week_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>morning</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>class_time_of_day_choices</t>
+          <t>class_day_of_week_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>afternoon</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>class_time_of_day_choices</t>
+          <t>class_day_of_week_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>evening</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>monday</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1811,437 +1811,216 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>tuesday</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>class_day_of_week_choices</t>
+          <t>class_duration_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>wednesday</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>class_day_of_week_choices</t>
+          <t>class_duration_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>thursday</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>class_day_of_week_choices</t>
+          <t>class_duration_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>friday</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>class_day_of_week_choices</t>
+          <t>class_frequency_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>saturday</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>class_day_of_week_choices</t>
+          <t>class_frequency_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>sunday</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>class_duration_choices</t>
+          <t>class_frequency_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>class_duration_choices</t>
+          <t>member_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>class_duration_choices</t>
+          <t>member_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>class_duration_choices</t>
+          <t>member_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>class_frequency_choices</t>
+          <t>staff_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>class_frequency_choices</t>
+          <t>staff_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>class_frequency_choices</t>
+          <t>staff_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>class_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>class_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>class_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>member_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>member_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>member_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>member_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>member_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>staff_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>staff_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>staff_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>staff_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>staff_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
